--- a/course-design-2/outputs/tables/ch5/44_stage26_2_negotiable_selection_bias.xlsx
+++ b/course-design-2/outputs/tables/ch5/44_stage26_2_negotiable_selection_bias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_结构对照_单值" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_卡方检验_单值" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_结构对照_多值" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_结论与口径" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="01_结构对照_单值" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_卡方检验_单值" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_结构对照_多值" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_结论与统计范围" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2745,7 +2745,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>实现口径</t>
+          <t>实现方式</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">

--- a/course-design-2/outputs/tables/ch5/44_stage26_2_negotiable_selection_bias.xlsx
+++ b/course-design-2/outputs/tables/ch5/44_stage26_2_negotiable_selection_bias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_结构对照_单值" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_卡方检验_单值" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_结构对照_多值" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_结论与统计范围" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_结构对照_单值" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_卡方检验_单值" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_结构对照_多值" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_结论与统计范围" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1115,7 +1115,6 @@
           <t>公司性质</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0.002227</v>
       </c>
@@ -2745,7 +2744,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>实现方式</t>
+          <t>实现口径</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
